--- a/02.dbms/03.테이블정의서.xlsx
+++ b/02.dbms/03.테이블정의서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MYCOM\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C12D88-6541-430A-A8FC-DD63F90585ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030BB64A-80C4-4D95-8BB6-4CC59163E8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="925" xr2:uid="{322AF230-7881-4F3B-AF7A-FBF94146604F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="925" activeTab="2" xr2:uid="{322AF230-7881-4F3B-AF7A-FBF94146604F}"/>
   </bookViews>
   <sheets>
     <sheet name="STORE" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="97">
   <si>
     <t>테이블 정의서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,313 +91,329 @@
     <t>테이블 설명</t>
   </si>
   <si>
+    <t>REVIEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메뉴 상세 정보 </t>
+  </si>
+  <si>
+    <t>AREA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STORE_CODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CATEGORY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STORE_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUSINESS_HOURS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMENITY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STORE_IMAGE_URL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PN_RATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDRESS_DO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDRESS_JI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PARKING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MENU_CODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MENU_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BEST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(255)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MENU_PRICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PK,AI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">메뉴 관리 번호 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">네이버 플레이스 일련번호 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴가격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">언급수 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대표메뉴여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WORD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">단어 상세 테이블 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WORD_CODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REVIEW_CODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WORD_PN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR(1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">관리번호 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">리뷰관리번호 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">단어 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">리뷰 긍부정 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">업체 상세 정보 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LNG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECIMAL(10,7)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DECIMAL(11,7)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLOAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIQUE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">업체명 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소(도로명)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소(지번)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">업체 전화번호 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">영업시간 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">주차여부 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">편의성(예:  단체, 포장, 배달) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도(위도)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도(경도)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카테고리(한식,양식)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>별점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업체 사진 URL(주소)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">상권 구분 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업체 긍정율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CONTENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WRITTEN_DT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YEAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PN_SCORE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">리뷰 정보 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">리뷰 코드 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업체 코드 FK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">리뷰 본문 </t>
-  </si>
-  <si>
-    <t>REVIEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(방문자 리뷰 + 블로그 리뷰) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">리뷰 관리 번호 </t>
-  </si>
-  <si>
-    <t>USER_REVIEW_RAW의 방문자 리뷰 번호</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOG_REVIEW_RAW의 블로그 리뷰 번호 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">저장일시 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">리뷰 작성일 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">감성 분석 여부 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">메뉴 상세 정보 </t>
-  </si>
-  <si>
-    <t>AREA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STORE_CODE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CATEGORY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STORE_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUSINESS_HOURS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AMENITY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STORE_IMAGE_URL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PN_RATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADDRESS_DO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADDRESS_JI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PARKING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MENU_CODE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MENU_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BEST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VARCHAR(30)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VARCHAR(255)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MENU_PRICE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BOOLEAN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PK,AI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">메뉴 관리 번호 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">네이버 플레이스 일련번호 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메뉴명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메뉴가격</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">언급수 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대표메뉴여부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WORD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">단어 상세 테이블 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WORD_CODE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REVIEW_CODE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WORD_PN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CHAR(1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">관리번호 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">리뷰관리번호 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">단어 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">리뷰 긍부정 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">업체 상세 정보 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEXT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LAT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LNG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STAR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DECIMAL(10,7)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DECIMAL(11,7)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FLOAT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNIQUE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">업체명 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주소(도로명)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주소(지번)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">업체 전화번호 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">영업시간 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">주차여부 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">편의성(예:  단체, 포장, 배달) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지도(위도)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지도(경도)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카테고리(한식,양식)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>별점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>업체 사진 URL(주소)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">상권 구분 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>업체 긍정율</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CONTENT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WRITTEN_DT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YEAR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MONTH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DAY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REvIEW_PN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PN_SCORE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">리뷰 작성 날짜 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REVIEW_PN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리뷰 긍 부정(P/N)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">긍부정 상세 점수 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -589,10 +605,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -600,18 +628,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -941,14 +957,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-    </row>
-    <row r="2" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -959,14 +975,14 @@
         <v>2</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -984,13 +1000,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -998,169 +1014,169 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1243,12 +1259,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -1261,20 +1277,20 @@
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="17" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1294,78 +1310,78 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
-        <v>40</v>
+      <c r="A10" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1469,38 +1485,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="20" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1520,7 +1536,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
@@ -1529,93 +1545,99 @@
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1642,38 +1664,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="17" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1693,52 +1715,52 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">

--- a/02.dbms/03.테이블정의서.xlsx
+++ b/02.dbms/03.테이블정의서.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MYCOM\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jreview\02.dbms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030BB64A-80C4-4D95-8BB6-4CC59163E8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE374D62-FE33-442A-91D4-277E20F65A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="925" activeTab="2" xr2:uid="{322AF230-7881-4F3B-AF7A-FBF94146604F}"/>
+    <workbookView xWindow="7560" yWindow="7425" windowWidth="13260" windowHeight="9495" tabRatio="925" activeTab="2" xr2:uid="{322AF230-7881-4F3B-AF7A-FBF94146604F}"/>
   </bookViews>
   <sheets>
     <sheet name="STORE" sheetId="1" r:id="rId1"/>
-    <sheet name="menu" sheetId="27" r:id="rId2"/>
-    <sheet name="review" sheetId="4" r:id="rId3"/>
+    <sheet name="MENU" sheetId="27" r:id="rId2"/>
+    <sheet name="REVIEW" sheetId="4" r:id="rId3"/>
     <sheet name="WORD" sheetId="14" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="96">
   <si>
     <t>테이블 정의서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -249,10 +249,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">리뷰 긍부정 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">업체 상세 정보 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -325,10 +321,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>카테고리(한식,양식)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>별점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -377,22 +369,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">리뷰 코드 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>업체 코드 FK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">리뷰 본문 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">리뷰 작성 날짜 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>년</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -409,11 +389,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>리뷰 긍 부정(P/N)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">긍부정 상세 점수 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">리뷰 긍부정(P,N,J) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리뷰 긍 부정(P,N,J)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">리뷰 관리 번호 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리뷰 작성일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카테고리(한식,일식)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -975,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1006,7 +1002,7 @@
         <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -1021,7 +1017,7 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1033,7 +1029,7 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1045,7 +1041,7 @@
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1056,7 +1052,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1064,11 +1060,11 @@
         <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1080,7 +1076,7 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1092,31 +1088,31 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1128,19 +1124,19 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="2" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1148,11 +1144,11 @@
         <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1164,7 +1160,7 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1172,11 +1168,11 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1503,7 +1499,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1545,7 +1541,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1556,88 +1552,88 @@
         <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1756,7 @@
         <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">

--- a/02.dbms/03.테이블정의서.xlsx
+++ b/02.dbms/03.테이블정의서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jreview\02.dbms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JReview\02.dbms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE374D62-FE33-442A-91D4-277E20F65A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F554E72-1126-401B-996B-25F62C6C5989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7560" yWindow="7425" windowWidth="13260" windowHeight="9495" tabRatio="925" activeTab="2" xr2:uid="{322AF230-7881-4F3B-AF7A-FBF94146604F}"/>
+    <workbookView xWindow="6705" yWindow="2040" windowWidth="14715" windowHeight="12990" tabRatio="925" xr2:uid="{322AF230-7881-4F3B-AF7A-FBF94146604F}"/>
   </bookViews>
   <sheets>
     <sheet name="STORE" sheetId="1" r:id="rId1"/>
@@ -281,10 +281,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>UNIQUE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">업체명 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -410,6 +406,10 @@
   </si>
   <si>
     <t>카테고리(한식,일식)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PK,UNIQUE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1002,7 +1002,7 @@
         <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1052,7 +1052,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1499,7 +1499,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1541,7 +1541,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1552,7 +1552,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>41</v>
@@ -1560,80 +1560,80 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1756,7 +1756,7 @@
         <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">

--- a/02.dbms/03.테이블정의서.xlsx
+++ b/02.dbms/03.테이블정의서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JReview\02.dbms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F554E72-1126-401B-996B-25F62C6C5989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4767BF3-B987-4AB5-8302-5BF8F0141F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6705" yWindow="2040" windowWidth="14715" windowHeight="12990" tabRatio="925" xr2:uid="{322AF230-7881-4F3B-AF7A-FBF94146604F}"/>
+    <workbookView xWindow="12525" yWindow="2730" windowWidth="14715" windowHeight="12990" tabRatio="925" xr2:uid="{322AF230-7881-4F3B-AF7A-FBF94146604F}"/>
   </bookViews>
   <sheets>
     <sheet name="STORE" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="98">
   <si>
     <t>테이블 정의서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -410,6 +410,14 @@
   </si>
   <si>
     <t>PK,UNIQUE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI_REPORT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 분석 리포트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1176,10 +1184,16 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
